--- a/product_selector_out/STM32WB0 series - diff.xlsx
+++ b/product_selector_out/STM32WB0 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="18">
@@ -1096,22 +1096,18 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Arm Cortex-M0+</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1123,13 +1119,13 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1138,31 +1134,8 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>STM32WB05TN</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A18:E40"/>
+  <autoFilter ref="A18:E39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32WB0 series - diff.xlsx
+++ b/product_selector_out/STM32WB0 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="18">
@@ -1096,18 +1096,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Arm Cortex-M0+</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -1119,23 +1123,46 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32WB05TN</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E39"/>
+  <autoFilter ref="A18:E40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32WB0 series - diff.xlsx
+++ b/product_selector_out/STM32WB0 series - diff.xlsx
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>670</v>
+        <v>680</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>649</v>
+        <v>659</v>
       </c>
     </row>
     <row r="18">
